--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6691-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6691-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{36352E5C-19A6-4E33-A4B4-2F416E52DFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A359BFF-E057-400A-98A1-F3357FAC09A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{82B0E570-B12C-44F3-A3D0-1D15D95B9B4E}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{23A1FA5E-39FB-496E-8100-D27AF75BB970}"/>
   </bookViews>
   <sheets>
     <sheet name="6691-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1442,25 +1442,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD5C62B1-3309-46A5-9FDD-6A4521CAEC15}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77E2971E-A810-40D1-9761-63942F431DCD}">
   <dimension ref="A1:R16"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="9.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="7" width="10.375" customWidth="1"/>
+    <col min="8" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1488,7 +1488,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1518,7 +1518,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1564,7 +1564,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1614,7 +1614,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1668,7 +1668,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="39">
         <v>2024</v>
       </c>
@@ -1722,7 +1722,7 @@
         <v>4.34</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="37">
         <v>2023</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>5.57</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2022</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>8.2799999999999994</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="37">
         <v>2021</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>26</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="39">
         <v>2020</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>5.57</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>26</v>
       </c>
@@ -2050,7 +2050,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>26</v>
       </c>
@@ -2106,7 +2106,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>26</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>5.57</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>2019</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="39" t="s">
         <v>33</v>
       </c>
